--- a/code/resultados/NWJSSP_OADG_NEH(SwapFirstImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(SwapFirstImprovement).xlsx
@@ -15,6 +15,8 @@
     <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j100_m10_1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="tai_j100_m10_1r" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +430,7 @@
         <v>309</v>
       </c>
       <c r="B1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
@@ -449,6 +451,428 @@
       </c>
       <c r="F2" t="n">
         <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6786530</v>
+      </c>
+      <c r="B1" t="n">
+        <v>176301</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+      <c r="K1" t="inlineStr"/>
+      <c r="L1" t="inlineStr"/>
+      <c r="M1" t="inlineStr"/>
+      <c r="N1" t="inlineStr"/>
+      <c r="O1" t="inlineStr"/>
+      <c r="P1" t="inlineStr"/>
+      <c r="Q1" t="inlineStr"/>
+      <c r="R1" t="inlineStr"/>
+      <c r="S1" t="inlineStr"/>
+      <c r="T1" t="inlineStr"/>
+      <c r="U1" t="inlineStr"/>
+      <c r="V1" t="inlineStr"/>
+      <c r="W1" t="inlineStr"/>
+      <c r="X1" t="inlineStr"/>
+      <c r="Y1" t="inlineStr"/>
+      <c r="Z1" t="inlineStr"/>
+      <c r="AA1" t="inlineStr"/>
+      <c r="AB1" t="inlineStr"/>
+      <c r="AC1" t="inlineStr"/>
+      <c r="AD1" t="inlineStr"/>
+      <c r="AE1" t="inlineStr"/>
+      <c r="AF1" t="inlineStr"/>
+      <c r="AG1" t="inlineStr"/>
+      <c r="AH1" t="inlineStr"/>
+      <c r="AI1" t="inlineStr"/>
+      <c r="AJ1" t="inlineStr"/>
+      <c r="AK1" t="inlineStr"/>
+      <c r="AL1" t="inlineStr"/>
+      <c r="AM1" t="inlineStr"/>
+      <c r="AN1" t="inlineStr"/>
+      <c r="AO1" t="inlineStr"/>
+      <c r="AP1" t="inlineStr"/>
+      <c r="AQ1" t="inlineStr"/>
+      <c r="AR1" t="inlineStr"/>
+      <c r="AS1" t="inlineStr"/>
+      <c r="AT1" t="inlineStr"/>
+      <c r="AU1" t="inlineStr"/>
+      <c r="AV1" t="inlineStr"/>
+      <c r="AW1" t="inlineStr"/>
+      <c r="AX1" t="inlineStr"/>
+      <c r="AY1" t="inlineStr"/>
+      <c r="AZ1" t="inlineStr"/>
+      <c r="BA1" t="inlineStr"/>
+      <c r="BB1" t="inlineStr"/>
+      <c r="BC1" t="inlineStr"/>
+      <c r="BD1" t="inlineStr"/>
+      <c r="BE1" t="inlineStr"/>
+      <c r="BF1" t="inlineStr"/>
+      <c r="BG1" t="inlineStr"/>
+      <c r="BH1" t="inlineStr"/>
+      <c r="BI1" t="inlineStr"/>
+      <c r="BJ1" t="inlineStr"/>
+      <c r="BK1" t="inlineStr"/>
+      <c r="BL1" t="inlineStr"/>
+      <c r="BM1" t="inlineStr"/>
+      <c r="BN1" t="inlineStr"/>
+      <c r="BO1" t="inlineStr"/>
+      <c r="BP1" t="inlineStr"/>
+      <c r="BQ1" t="inlineStr"/>
+      <c r="BR1" t="inlineStr"/>
+      <c r="BS1" t="inlineStr"/>
+      <c r="BT1" t="inlineStr"/>
+      <c r="BU1" t="inlineStr"/>
+      <c r="BV1" t="inlineStr"/>
+      <c r="BW1" t="inlineStr"/>
+      <c r="BX1" t="inlineStr"/>
+      <c r="BY1" t="inlineStr"/>
+      <c r="BZ1" t="inlineStr"/>
+      <c r="CA1" t="inlineStr"/>
+      <c r="CB1" t="inlineStr"/>
+      <c r="CC1" t="inlineStr"/>
+      <c r="CD1" t="inlineStr"/>
+      <c r="CE1" t="inlineStr"/>
+      <c r="CF1" t="inlineStr"/>
+      <c r="CG1" t="inlineStr"/>
+      <c r="CH1" t="inlineStr"/>
+      <c r="CI1" t="inlineStr"/>
+      <c r="CJ1" t="inlineStr"/>
+      <c r="CK1" t="inlineStr"/>
+      <c r="CL1" t="inlineStr"/>
+      <c r="CM1" t="inlineStr"/>
+      <c r="CN1" t="inlineStr"/>
+      <c r="CO1" t="inlineStr"/>
+      <c r="CP1" t="inlineStr"/>
+      <c r="CQ1" t="inlineStr"/>
+      <c r="CR1" t="inlineStr"/>
+      <c r="CS1" t="inlineStr"/>
+      <c r="CT1" t="inlineStr"/>
+      <c r="CU1" t="inlineStr"/>
+      <c r="CV1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>53972</v>
+      </c>
+      <c r="B2" t="n">
+        <v>47051</v>
+      </c>
+      <c r="C2" t="n">
+        <v>48951</v>
+      </c>
+      <c r="D2" t="n">
+        <v>116251</v>
+      </c>
+      <c r="E2" t="n">
+        <v>105909</v>
+      </c>
+      <c r="F2" t="n">
+        <v>66654</v>
+      </c>
+      <c r="G2" t="n">
+        <v>107293</v>
+      </c>
+      <c r="H2" t="n">
+        <v>94577</v>
+      </c>
+      <c r="I2" t="n">
+        <v>72178</v>
+      </c>
+      <c r="J2" t="n">
+        <v>55681</v>
+      </c>
+      <c r="K2" t="n">
+        <v>33086</v>
+      </c>
+      <c r="L2" t="n">
+        <v>87548</v>
+      </c>
+      <c r="M2" t="n">
+        <v>9150</v>
+      </c>
+      <c r="N2" t="n">
+        <v>67940</v>
+      </c>
+      <c r="O2" t="n">
+        <v>44138</v>
+      </c>
+      <c r="P2" t="n">
+        <v>12255</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>49689</v>
+      </c>
+      <c r="R2" t="n">
+        <v>49230</v>
+      </c>
+      <c r="S2" t="n">
+        <v>39417</v>
+      </c>
+      <c r="T2" t="n">
+        <v>32233</v>
+      </c>
+      <c r="U2" t="n">
+        <v>128001</v>
+      </c>
+      <c r="V2" t="n">
+        <v>124714</v>
+      </c>
+      <c r="W2" t="n">
+        <v>95618</v>
+      </c>
+      <c r="X2" t="n">
+        <v>112164</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>131546</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>42226</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>36933</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>69810</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>12598</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>62818</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>3937</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>118482</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>104735</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>59353</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>28799</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>98504</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>80411</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>96381</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>116653</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>78516</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>6638</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>21308</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>110228</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>125430</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>44103</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>73059</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1641</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>23531</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>109252</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>56980</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>127987</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>76335</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>42755</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>35187</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>16947</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>27309</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>91940</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3139</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>38329</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>36533</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>30912</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>93</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>64975</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>74051</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>100434</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>80497</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>60044</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>83911</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>92892</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>20828</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>83481</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>93118</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>52584</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>54758</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>85057</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>110269</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>48010</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>122752</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>62176</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>65275</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>24971</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>32372</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>90234</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>15166</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>75812</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>12136</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>9256</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>119970</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>115007</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>101168</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>2142</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>5212</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>56071</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>28358</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>86651</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>116638</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>16327</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>102388</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>21675</v>
       </c>
     </row>
   </sheetData>
@@ -512,7 +936,7 @@
         <v>10384</v>
       </c>
       <c r="B1" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2">
@@ -566,7 +990,7 @@
         <v>11692</v>
       </c>
       <c r="B1" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2">
@@ -620,7 +1044,7 @@
         <v>19770</v>
       </c>
       <c r="B1" t="n">
-        <v>90</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
@@ -704,7 +1128,7 @@
         <v>20507</v>
       </c>
       <c r="B1" t="n">
-        <v>141</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2">
@@ -788,7 +1212,7 @@
         <v>111153</v>
       </c>
       <c r="B1" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2">
@@ -842,16 +1266,8 @@
         <v>114471</v>
       </c>
       <c r="B1" t="n">
-        <v>13</v>
-      </c>
-      <c r="C1" t="inlineStr"/>
-      <c r="D1" t="inlineStr"/>
-      <c r="E1" t="inlineStr"/>
-      <c r="F1" t="inlineStr"/>
-      <c r="G1" t="inlineStr"/>
-      <c r="H1" t="inlineStr"/>
-      <c r="I1" t="inlineStr"/>
-      <c r="J1" t="inlineStr"/>
+        <v>8</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -883,6 +1299,330 @@
       </c>
       <c r="J2" t="n">
         <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>6926870</v>
+      </c>
+      <c r="B1" t="n">
+        <v>56459</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>56613</v>
+      </c>
+      <c r="B2" t="n">
+        <v>93601</v>
+      </c>
+      <c r="C2" t="n">
+        <v>48708</v>
+      </c>
+      <c r="D2" t="n">
+        <v>31185</v>
+      </c>
+      <c r="E2" t="n">
+        <v>15658</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15625</v>
+      </c>
+      <c r="G2" t="n">
+        <v>41686</v>
+      </c>
+      <c r="H2" t="n">
+        <v>124711</v>
+      </c>
+      <c r="I2" t="n">
+        <v>131715</v>
+      </c>
+      <c r="J2" t="n">
+        <v>48029</v>
+      </c>
+      <c r="K2" t="n">
+        <v>15518</v>
+      </c>
+      <c r="L2" t="n">
+        <v>108285</v>
+      </c>
+      <c r="M2" t="n">
+        <v>90044</v>
+      </c>
+      <c r="N2" t="n">
+        <v>9198</v>
+      </c>
+      <c r="O2" t="n">
+        <v>72064</v>
+      </c>
+      <c r="P2" t="n">
+        <v>28909</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>99900</v>
+      </c>
+      <c r="R2" t="n">
+        <v>81408</v>
+      </c>
+      <c r="S2" t="n">
+        <v>55322</v>
+      </c>
+      <c r="T2" t="n">
+        <v>26416</v>
+      </c>
+      <c r="U2" t="n">
+        <v>99822</v>
+      </c>
+      <c r="V2" t="n">
+        <v>96681</v>
+      </c>
+      <c r="W2" t="n">
+        <v>132511</v>
+      </c>
+      <c r="X2" t="n">
+        <v>118263</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>117533</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>7142</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>70165</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>75179</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>7426</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>33250</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>12900</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>72921</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>53919</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>106637</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>20707</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>47041</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>933</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>59986</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>52595</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>87098</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>78234</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>51022</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>44339</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>97318</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>6372</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>87430</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>76138</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>118757</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>64788</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>34988</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>81644</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>137071</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>91711</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>26948</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>101498</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>36316</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>113838</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>59494</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>29173</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>135407</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>55236</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>2057</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>126437</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>93852</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>67852</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>128061</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>129845</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>20522</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>112600</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>79546</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4476</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>120184</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>62639</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>12895</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>102531</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>65771</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>36251</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>42246</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>39525</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>103768</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>108893</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>114835</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>21708</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>9365</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>24472</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>85705</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>68864</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>32223</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>19568</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>111612</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>83250</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>52625</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>47141</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>124024</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>122137</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>37628</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>11889</v>
       </c>
     </row>
   </sheetData>

--- a/code/resultados/NWJSSP_OADG_NEH(SwapFirstImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(SwapFirstImprovement).xlsx
@@ -472,7 +472,7 @@
         <v>6786530</v>
       </c>
       <c r="B1" t="n">
-        <v>176301</v>
+        <v>208178</v>
       </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
@@ -936,7 +936,7 @@
         <v>10384</v>
       </c>
       <c r="B1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
@@ -990,7 +990,7 @@
         <v>11692</v>
       </c>
       <c r="B1" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2">
@@ -1044,7 +1044,7 @@
         <v>19770</v>
       </c>
       <c r="B1" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="2">
@@ -1128,7 +1128,7 @@
         <v>20507</v>
       </c>
       <c r="B1" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2">
@@ -1212,7 +1212,7 @@
         <v>111153</v>
       </c>
       <c r="B1" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2">
@@ -1320,7 +1320,7 @@
         <v>6926870</v>
       </c>
       <c r="B1" t="n">
-        <v>56459</v>
+        <v>55486</v>
       </c>
     </row>
     <row r="2">

--- a/code/resultados/NWJSSP_OADG_NEH(SwapFirstImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(SwapFirstImprovement).xlsx
@@ -1,45 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\clase\Desktop\OADG\Heuristica-Trabajo-2\code\resultados\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67FC4D14-CE0B-4D12-9467-0644E484A5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ft06" sheetId="1" r:id="rId1"/>
-    <sheet name="ft06r" sheetId="2" r:id="rId2"/>
-    <sheet name="ft10" sheetId="3" r:id="rId3"/>
-    <sheet name="ft10r" sheetId="4" r:id="rId4"/>
-    <sheet name="ft20" sheetId="5" r:id="rId5"/>
-    <sheet name="ft20r" sheetId="6" r:id="rId6"/>
-    <sheet name="tai_j10_m10_1" sheetId="7" r:id="rId7"/>
-    <sheet name="tai_j10_m10_1r" sheetId="8" r:id="rId8"/>
+    <sheet name="ft06" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ft06r" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="ft10" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ft10r" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ft20" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -58,21 +53,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -360,35 +414,39 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>309</v>
       </c>
-      <c r="B1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>15</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>15</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>36</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>43</v>
       </c>
     </row>
@@ -398,35 +456,39 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>324</v>
       </c>
-      <c r="B1">
+      <c r="B1" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>19</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>15</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>42</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>3</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>48</v>
       </c>
     </row>
@@ -436,47 +498,51 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>10384</v>
       </c>
-      <c r="B1">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>46</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>132</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>509</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1281</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1057</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>463</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>840</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>693</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>254</v>
       </c>
     </row>
@@ -486,47 +552,51 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>11692</v>
       </c>
-      <c r="B1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>658</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>380</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1142</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>1095</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1318</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>334</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>835</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>696</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>125</v>
       </c>
     </row>
@@ -536,77 +606,81 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>19770</v>
       </c>
-      <c r="B1">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" t="n">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>253</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>409</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>690</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>781</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1490</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>644</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>205</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>1553</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>1121</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>1649</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>14</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>1331</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>370</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>1021</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>312</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>118</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>1120</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>958</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>622</v>
       </c>
     </row>
@@ -616,77 +690,81 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:T2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>20507</v>
       </c>
-      <c r="B1">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>7</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1075</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>1344</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>1228</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>1638</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>1651</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>433</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>825</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>170</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="n">
         <v>660</v>
       </c>
-      <c r="L2">
+      <c r="L2" t="n">
         <v>531</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="n">
         <v>1479</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="n">
         <v>316</v>
       </c>
-      <c r="O2">
+      <c r="O2" t="n">
         <v>955</v>
       </c>
-      <c r="P2">
+      <c r="P2" t="n">
         <v>959</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" t="n">
         <v>1271</v>
       </c>
-      <c r="R2">
+      <c r="R2" t="n">
         <v>681</v>
       </c>
-      <c r="S2">
+      <c r="S2" t="n">
         <v>101</v>
       </c>
-      <c r="T2">
+      <c r="T2" t="n">
         <v>74</v>
       </c>
     </row>
@@ -696,47 +774,51 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>111153</v>
       </c>
-      <c r="B1">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>8464</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>1802</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>11833</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>2649</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>4394</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>4248</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>10370</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>9685</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>4953</v>
       </c>
     </row>
@@ -746,47 +828,59 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A1">
+    <row r="1">
+      <c r="A1" t="n">
         <v>114471</v>
       </c>
-      <c r="B1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2">
+      <c r="B1" t="n">
+        <v>13</v>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+      <c r="F1" t="inlineStr"/>
+      <c r="G1" t="inlineStr"/>
+      <c r="H1" t="inlineStr"/>
+      <c r="I1" t="inlineStr"/>
+      <c r="J1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
         <v>712</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="n">
         <v>2031</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="n">
         <v>848</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>12861</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="n">
         <v>5089</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="n">
         <v>9463</v>
       </c>
-      <c r="G2">
+      <c r="G2" t="n">
         <v>9091</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="n">
         <v>7252</v>
       </c>
-      <c r="I2">
+      <c r="I2" t="n">
         <v>14369</v>
       </c>
-      <c r="J2">
+      <c r="J2" t="n">
         <v>0</v>
       </c>
     </row>

--- a/code/resultados/NWJSSP_OADG_NEH(SwapFirstImprovement).xlsx
+++ b/code/resultados/NWJSSP_OADG_NEH(SwapFirstImprovement).xlsx
@@ -14,6 +14,8 @@
     <sheet name="ft20r" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="tai_j10_m10_1" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="tai_j10_m10_1r" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="tai_j100_m100_1" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="tai_j100_m100_1r" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -424,7 +426,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B1" t="n">
         <v>3</v>
@@ -432,22 +434,346 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C2" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2" t="n">
         <v>0</v>
       </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>43676166</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3628088</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>63399</v>
+      </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>743061</v>
       </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>432713</v>
       </c>
       <c r="D2" t="n">
-        <v>36</v>
+        <v>98110</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>55144</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>306907</v>
+      </c>
+      <c r="G2" t="n">
+        <v>823951</v>
+      </c>
+      <c r="H2" t="n">
+        <v>643203</v>
+      </c>
+      <c r="I2" t="n">
+        <v>95858</v>
+      </c>
+      <c r="J2" t="n">
+        <v>256466</v>
+      </c>
+      <c r="K2" t="n">
+        <v>835858</v>
+      </c>
+      <c r="L2" t="n">
+        <v>311706</v>
+      </c>
+      <c r="M2" t="n">
+        <v>497458</v>
+      </c>
+      <c r="N2" t="n">
+        <v>648106</v>
+      </c>
+      <c r="O2" t="n">
+        <v>627283</v>
+      </c>
+      <c r="P2" t="n">
+        <v>472871</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>293217</v>
+      </c>
+      <c r="R2" t="n">
+        <v>267858</v>
+      </c>
+      <c r="S2" t="n">
+        <v>575981</v>
+      </c>
+      <c r="T2" t="n">
+        <v>159742</v>
+      </c>
+      <c r="U2" t="n">
+        <v>42097</v>
+      </c>
+      <c r="V2" t="n">
+        <v>837137</v>
+      </c>
+      <c r="W2" t="n">
+        <v>290527</v>
+      </c>
+      <c r="X2" t="n">
+        <v>233860</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>90341</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>491702</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>701525</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>407122</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>791501</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>751043</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>563092</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>359570</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>484681</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>590775</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>146332</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>669893</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>151978</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>368094</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>242073</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>377046</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>139562</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>705</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>330093</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>271206</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>712088</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3102</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>21013</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>480034</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>92765</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>188184</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>303741</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>601339</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>251228</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>397117</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>214578</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>165914</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>12994</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>753437</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>199103</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>349509</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>624383</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>464821</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>780535</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>186995</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>66036</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>410115</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>149421</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>435299</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>555746</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>64661</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>450540</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>584483</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>206096</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>723315</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>785380</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>16033</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>131092</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>589182</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>428507</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>118863</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>663712</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>511838</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>22017</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>128971</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>250553</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>60932</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>323868</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>525123</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>534830</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>652196</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>535259</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>202111</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>699425</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>784333</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>722252</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>360524</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>455954</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>370648</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>814456</v>
       </c>
     </row>
   </sheetData>
@@ -466,7 +792,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>324</v>
+        <v>349</v>
       </c>
       <c r="B1" t="n">
         <v>1</v>
@@ -474,22 +800,22 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="B2" t="n">
-        <v>19</v>
-      </c>
       <c r="C2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="F2" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -508,10 +834,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>10384</v>
+        <v>10031</v>
       </c>
       <c r="B1" t="n">
-        <v>19</v>
+        <v>89</v>
       </c>
     </row>
     <row r="2">
@@ -519,31 +845,31 @@
         <v>46</v>
       </c>
       <c r="B2" t="n">
-        <v>132</v>
+        <v>201</v>
       </c>
       <c r="C2" t="n">
-        <v>509</v>
+        <v>776</v>
       </c>
       <c r="D2" t="n">
-        <v>1281</v>
+        <v>360</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1057</v>
+        <v>1079</v>
       </c>
       <c r="G2" t="n">
-        <v>463</v>
+        <v>561</v>
       </c>
       <c r="H2" t="n">
-        <v>840</v>
+        <v>613</v>
       </c>
       <c r="I2" t="n">
-        <v>693</v>
+        <v>84</v>
       </c>
       <c r="J2" t="n">
-        <v>254</v>
+        <v>1202</v>
       </c>
     </row>
   </sheetData>
@@ -562,42 +888,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>11692</v>
+        <v>10378</v>
       </c>
       <c r="B1" t="n">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>658</v>
+        <v>299</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>380</v>
+        <v>811</v>
       </c>
       <c r="D2" t="n">
-        <v>1142</v>
+        <v>1265</v>
       </c>
       <c r="E2" t="n">
-        <v>1095</v>
+        <v>616</v>
       </c>
       <c r="F2" t="n">
-        <v>1318</v>
+        <v>179</v>
       </c>
       <c r="G2" t="n">
-        <v>334</v>
+        <v>9</v>
       </c>
       <c r="H2" t="n">
-        <v>835</v>
+        <v>375</v>
       </c>
       <c r="I2" t="n">
-        <v>696</v>
+        <v>989</v>
       </c>
       <c r="J2" t="n">
-        <v>125</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -616,72 +942,72 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>19770</v>
+        <v>18296</v>
       </c>
       <c r="B1" t="n">
-        <v>75</v>
+        <v>515</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>253</v>
+        <v>195</v>
       </c>
       <c r="B2" t="n">
-        <v>409</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>690</v>
+        <v>1379</v>
       </c>
       <c r="D2" t="n">
-        <v>781</v>
+        <v>597</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2" t="n">
-        <v>1490</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>644</v>
+        <v>738</v>
       </c>
       <c r="H2" t="n">
-        <v>205</v>
+        <v>380</v>
       </c>
       <c r="I2" t="n">
-        <v>1553</v>
+        <v>1580</v>
       </c>
       <c r="J2" t="n">
-        <v>1121</v>
+        <v>972</v>
       </c>
       <c r="K2" t="n">
-        <v>1649</v>
+        <v>269</v>
       </c>
       <c r="L2" t="n">
-        <v>14</v>
+        <v>282</v>
       </c>
       <c r="M2" t="n">
-        <v>1331</v>
+        <v>569</v>
       </c>
       <c r="N2" t="n">
-        <v>370</v>
+        <v>1118</v>
       </c>
       <c r="O2" t="n">
-        <v>1021</v>
+        <v>872</v>
       </c>
       <c r="P2" t="n">
-        <v>312</v>
+        <v>1365</v>
       </c>
       <c r="Q2" t="n">
-        <v>118</v>
+        <v>489</v>
       </c>
       <c r="R2" t="n">
-        <v>1120</v>
+        <v>971</v>
       </c>
       <c r="S2" t="n">
-        <v>958</v>
+        <v>808</v>
       </c>
       <c r="T2" t="n">
-        <v>622</v>
+        <v>556</v>
       </c>
     </row>
   </sheetData>
@@ -700,10 +1026,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>20507</v>
+        <v>17814</v>
       </c>
       <c r="B1" t="n">
-        <v>125</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="2">
@@ -711,61 +1037,61 @@
         <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>1075</v>
+        <v>1446</v>
       </c>
       <c r="C2" t="n">
-        <v>1344</v>
+        <v>1146</v>
       </c>
       <c r="D2" t="n">
-        <v>1228</v>
+        <v>745</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1638</v>
+        <v>1480</v>
       </c>
       <c r="G2" t="n">
-        <v>1651</v>
+        <v>299</v>
       </c>
       <c r="H2" t="n">
+        <v>211</v>
+      </c>
+      <c r="I2" t="n">
+        <v>647</v>
+      </c>
+      <c r="J2" t="n">
+        <v>924</v>
+      </c>
+      <c r="K2" t="n">
+        <v>78</v>
+      </c>
+      <c r="L2" t="n">
+        <v>113</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1306</v>
+      </c>
+      <c r="N2" t="n">
+        <v>632</v>
+      </c>
+      <c r="O2" t="n">
         <v>433</v>
       </c>
-      <c r="I2" t="n">
-        <v>825</v>
-      </c>
-      <c r="J2" t="n">
-        <v>170</v>
-      </c>
-      <c r="K2" t="n">
-        <v>660</v>
-      </c>
-      <c r="L2" t="n">
-        <v>531</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1479</v>
-      </c>
-      <c r="N2" t="n">
-        <v>316</v>
-      </c>
-      <c r="O2" t="n">
-        <v>955</v>
-      </c>
       <c r="P2" t="n">
+        <v>1132</v>
+      </c>
+      <c r="Q2" t="n">
         <v>959</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1271</v>
-      </c>
       <c r="R2" t="n">
-        <v>681</v>
+        <v>503</v>
       </c>
       <c r="S2" t="n">
-        <v>101</v>
+        <v>369</v>
       </c>
       <c r="T2" t="n">
-        <v>74</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
@@ -784,42 +1110,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>111153</v>
+        <v>108576</v>
       </c>
       <c r="B1" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>8464</v>
+        <v>8190</v>
       </c>
       <c r="B2" t="n">
-        <v>1802</v>
+        <v>11970</v>
       </c>
       <c r="C2" t="n">
-        <v>11833</v>
+        <v>6135</v>
       </c>
       <c r="D2" t="n">
-        <v>2649</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>6331</v>
       </c>
       <c r="F2" t="n">
-        <v>4394</v>
+        <v>9468</v>
       </c>
       <c r="G2" t="n">
-        <v>4248</v>
+        <v>1223</v>
       </c>
       <c r="H2" t="n">
-        <v>10370</v>
+        <v>1228</v>
       </c>
       <c r="I2" t="n">
-        <v>9685</v>
+        <v>3812</v>
       </c>
       <c r="J2" t="n">
-        <v>4953</v>
+        <v>7464</v>
       </c>
     </row>
   </sheetData>
@@ -838,10 +1164,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>114471</v>
+        <v>98735</v>
       </c>
       <c r="B1" t="n">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="C1" t="inlineStr"/>
       <c r="D1" t="inlineStr"/>
@@ -854,34 +1180,358 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>712</v>
+        <v>6527</v>
       </c>
       <c r="B2" t="n">
-        <v>2031</v>
+        <v>4350</v>
       </c>
       <c r="C2" t="n">
-        <v>848</v>
+        <v>4136</v>
       </c>
       <c r="D2" t="n">
-        <v>12861</v>
+        <v>11539</v>
       </c>
       <c r="E2" t="n">
-        <v>5089</v>
+        <v>2287</v>
       </c>
       <c r="F2" t="n">
-        <v>9463</v>
+        <v>7805</v>
       </c>
       <c r="G2" t="n">
-        <v>9091</v>
+        <v>22</v>
       </c>
       <c r="H2" t="n">
-        <v>7252</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>14369</v>
+        <v>8545</v>
       </c>
       <c r="J2" t="n">
+        <v>769</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:CV2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="n">
+        <v>44170627</v>
+      </c>
+      <c r="B1" t="n">
+        <v>3614057</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>93049</v>
+      </c>
+      <c r="B2" t="n">
+        <v>137075</v>
+      </c>
+      <c r="C2" t="n">
         <v>0</v>
+      </c>
+      <c r="D2" t="n">
+        <v>777779</v>
+      </c>
+      <c r="E2" t="n">
+        <v>717998</v>
+      </c>
+      <c r="F2" t="n">
+        <v>643361</v>
+      </c>
+      <c r="G2" t="n">
+        <v>572657</v>
+      </c>
+      <c r="H2" t="n">
+        <v>115801</v>
+      </c>
+      <c r="I2" t="n">
+        <v>286687</v>
+      </c>
+      <c r="J2" t="n">
+        <v>128286</v>
+      </c>
+      <c r="K2" t="n">
+        <v>835870</v>
+      </c>
+      <c r="L2" t="n">
+        <v>603160</v>
+      </c>
+      <c r="M2" t="n">
+        <v>441546</v>
+      </c>
+      <c r="N2" t="n">
+        <v>464997</v>
+      </c>
+      <c r="O2" t="n">
+        <v>247699</v>
+      </c>
+      <c r="P2" t="n">
+        <v>39522</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>756278</v>
+      </c>
+      <c r="R2" t="n">
+        <v>146536</v>
+      </c>
+      <c r="S2" t="n">
+        <v>452832</v>
+      </c>
+      <c r="T2" t="n">
+        <v>215226</v>
+      </c>
+      <c r="U2" t="n">
+        <v>314637</v>
+      </c>
+      <c r="V2" t="n">
+        <v>633682</v>
+      </c>
+      <c r="W2" t="n">
+        <v>495376</v>
+      </c>
+      <c r="X2" t="n">
+        <v>391710</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>74457</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>197444</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>420857</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>116131</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>508217</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>699598</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>414795</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>513653</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>223351</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>347537</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>243465</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>365433</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>547781</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>591251</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>617095</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>378355</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>795986</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>6257</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>201983</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>851638</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>747878</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>26129</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>97412</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>232698</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>48502</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>261864</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>337397</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>348845</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>718632</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>301622</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>792733</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>175100</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>530627</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>701989</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>183477</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>40748</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>413710</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>115440</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>16634</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>167790</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>266109</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>510273</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>311153</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>426804</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>813230</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>283553</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>141997</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>261849</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>342061</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>666559</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>421655</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>572531</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>479513</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>667585</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>821935</v>
+      </c>
+      <c r="CB2" t="n">
+        <v>741535</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>64163</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>690795</v>
+      </c>
+      <c r="CE2" t="n">
+        <v>623017</v>
+      </c>
+      <c r="CF2" t="n">
+        <v>90206</v>
+      </c>
+      <c r="CG2" t="n">
+        <v>162845</v>
+      </c>
+      <c r="CH2" t="n">
+        <v>750068</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>83086</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>2811</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>616698</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>290903</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>558785</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>452320</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>230363</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>58896</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>522382</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>378181</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>449524</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>795894</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>190432</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>545973</v>
       </c>
     </row>
   </sheetData>
